--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/los-lagos.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>8359.32</v>
+        <v>8341.23</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1830.78</v>
+        <v>1826.81</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>73699.33</v>
+        <v>73793.81</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>8031.22</v>
+        <v>7927.83</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3233.13</v>
+        <v>3224.21</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>6752.37</v>
+        <v>6835.47</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>30894.46</v>
+        <v>31297.62</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1026.53</v>
+        <v>1012.57</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2394.11</v>
+        <v>2411.95</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>20653.53</v>
+        <v>20949.06</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,68 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>509.47</v>
+        <v>510.64</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2324-1191-CM26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>38086.48</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/los-lagos.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1037-176-CM25</t>
+          <t>2324-689-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>Comercializadora TJB S.A.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.095.313-k</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>8341.23</v>
+        <v>1909.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1037-180-CM25</t>
+          <t>1037-176-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1826.81</v>
+        <v>8341.23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1126922-2962-CM25</t>
+          <t>1037-180-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SCANNO SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.055.785-2</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>73793.81</v>
+        <v>1826.81</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3888-165-CM26</t>
+          <t>1126922-2962-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.251.800-4</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>SCANNO SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.055.785-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7927.83</v>
+        <v>73793.81</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2297-336-CM26</t>
+          <t>3888-165-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.251.800-4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>Ilustre Municipalidad de San Juan de la Costa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3224.21</v>
+        <v>7927.83</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1079639-291-CM26</t>
+          <t>2297-336-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>6835.47</v>
+        <v>3224.21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3479-642-CM26</t>
+          <t>1079639-291-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,22 +895,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.220.600-2</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>SECCIÓN COMPRAS X ZONA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>31297.62</v>
+        <v>6835.47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2297-580-CM26</t>
+          <t>3479-642-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.220.600-2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1012.57</v>
+        <v>31297.62</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4832-287-CM26</t>
+          <t>2297-580-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,22 +1017,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.252.000-9</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD COCHAMO</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2411.95</v>
+        <v>1012.57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2324-723-CM26</t>
+          <t>4832-287-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.252.000-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>ILUSTRE MUNICIPALIDAD COCHAMO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>GIORGIO STEFANO RATTO ANDAUR</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>15.775.663-k</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>20949.06</v>
+        <v>2411.95</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1063538-5109-CM26</t>
+          <t>2324-723-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.602.260-1</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>HOSPITAL BASE OSORNO</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>GIORGIO STEFANO RATTO ANDAUR</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>15.775.663-k</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>510.64</v>
+        <v>20949.06</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2324-1191-CM26</t>
+          <t>1063538-5109-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.602.260-1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>HOSPITAL BASE OSORNO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,6 +1240,67 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
+        <v>510.64</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2324-1191-CM26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
         <v>38086.48</v>
       </c>
     </row>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/los-lagos.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/los-lagos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Los Lagos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Los Lagos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2324-689-CM25</t>
+          <t>2297-53-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Comercializadora TJB S.A.</t>
+          <t>DISTRIBUIDORA Y COMERCIALIZADORA SANTA ELIANA SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.095.313-k</t>
+          <t>77.544.929-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1909.75</v>
+        <v>31611.01</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1037-176-CM25</t>
+          <t>2297-102-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>FRANCISCO JAVIER GIACAMAN HASBUN CONFECCION Y BORDADOS EMPRESA INDIVID</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.238.721-2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>8341.23</v>
+        <v>8889.76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1037-180-CM25</t>
+          <t>2297-153-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>INVERSIONES SANTA FRANCISCA SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.721.515-9</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1826.81</v>
+        <v>7620.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1126922-2962-CM25</t>
+          <t>1063538-8710-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>61.602.260-1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>HOSPITAL BASE OSORNO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SCANNO SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.055.785-2</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>73793.81</v>
+        <v>364.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3888-165-CM26</t>
+          <t>1126922-334-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.251.800-4</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>SCANNO SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.055.785-2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>7927.83</v>
+        <v>16081.77</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2297-336-CM26</t>
+          <t>2297-251-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>ALEJANDRO IGLESIAS SOTO</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>8.751.811-6</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3224.21</v>
+        <v>1184.21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1079639-291-CM26</t>
+          <t>1126922-386-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>SCANNO SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>77.055.785-2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6835.47</v>
+        <v>72853.21000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3479-642-CM26</t>
+          <t>2297-345-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.220.600-2</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL MAULE LTDA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.287.511-k</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>31297.62</v>
+        <v>50490.06</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2297-580-CM26</t>
+          <t>2297-601-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1012.57</v>
+        <v>1828.12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4832-287-CM26</t>
+          <t>2324-689-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.252.000-9</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD COCHAMO</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>Comercializadora TJB S.A.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.095.313-k</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2411.95</v>
+        <v>1909.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2324-723-CM26</t>
+          <t>2852-391-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>GIORGIO STEFANO RATTO ANDAUR</t>
+          <t>SURTI VENTAS S.A.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15.775.663-k</t>
+          <t>76.462.500-5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>20949.06</v>
+        <v>4772.45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1063538-5109-CM26</t>
+          <t>2852-390-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,27 +1195,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.602.260-1</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>HOSPITAL BASE OSORNO</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>510.64</v>
+        <v>10860.15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2324-1191-CM26</t>
+          <t>1057539-18103-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,7 +1301,1410 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
+        <v>1180.21</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2324-930-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>78.094.280-0</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>769.52</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2324-956-CM25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>GIORGIO STEFANO RATTO ANDAUR</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>15.775.663-k</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>21326.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2297-1123-CM25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>69.210.100-6</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>4580.31</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2297-1124-CM25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>69.210.100-6</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>1156.62</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2324-1146-CM25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>12353.87</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3888-435-CM25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>69.251.800-4</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>76.566.610-4</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>15410.46</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3888-442-CM25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>69.251.800-4</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>FUNDACION VIVIENDA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>70.016.130-7</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>7917.57</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1037-180-CM25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>1826.81</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1037-176-CM25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>8341.23</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1126922-2962-CM25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>62.000.800-1</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>SCANNO SPA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>77.055.785-2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>73793.81</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3888-165-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>69.251.800-4</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>7927.83</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2297-336-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>69.210.100-6</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>3224.21</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1079639-291-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>61.979.300-5</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS X ZONA</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>76.730.550-8</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>6835.47</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3479-642-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>69.220.600-2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>76.566.610-4</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>31297.62</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2297-580-CM26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>69.210.100-6</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>1012.57</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>4832-287-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>69.252.000-9</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD COCHAMO</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>2411.95</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2324-723-CM26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>GIORGIO STEFANO RATTO ANDAUR</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>15.775.663-k</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>20949.06</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1063538-5109-CM26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>61.602.260-1</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>HOSPITAL BASE OSORNO</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Hales Hnos y Cia Ltda</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>510.64</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2324-1188-CM26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>2610.76</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2324-1189-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>10302.03</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2324-1191-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
         <v>38086.48</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2324-1192-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>33859</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2297-1126-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>69.210.100-6</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>3167.87</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/los-lagos.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1124,7 +1124,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2852-391-CM25</t>
+          <t>2852-390-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SURTI VENTAS S.A.</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.462.500-5</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4772.45</v>
+        <v>10860.15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2852-390-CM25</t>
+          <t>2852-391-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>SURTI VENTAS S.A.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.462.500-5</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>10860.15</v>
+        <v>4772.45</v>
       </c>
     </row>
     <row r="14">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2705,6 +2705,189 @@
       </c>
       <c r="M37" s="2" t="n">
         <v>3167.87</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1057539-7016-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>1911.98</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1057539-7221-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Hales Hnos y Cia Ltda</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>3250.77</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1057539-7527-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Hales Hnos y Cia Ltda</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>26160.54</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/los-lagos.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/los-lagos.xlsx
@@ -562,7 +562,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>77.721.515-9</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +997,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1062,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1371,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1497,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1562,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1627,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1814,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1879,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2005,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2070,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2257,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2322,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2570,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/los-lagos.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2950,6 +2950,128 @@
         <v>26160.54</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2324-1398-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>4645.09</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2297-1321-CM26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>69.210.100-6</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>6340.64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/los-lagos.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/los-lagos.xlsx
@@ -2168,7 +2168,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
